--- a/docs/page-copy/05-视频目录-灵体医学.xlsx
+++ b/docs/page-copy/05-视频目录-灵体医学.xlsx
@@ -486,7 +486,7 @@
         <v>Part of the video of the general outline of woos spirit medicine has been filmed as the content of the second season video</v>
       </c>
       <c r="E4" t="str">
-        <v>已拍摄灵魂医学总纲部分视频为第2季视频内容</v>
+        <v>已拍摄灵魂医学总纲部分视频，为第 2 季视频内容</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -811,7 +811,7 @@
         <v>File 2-1 Abstract of Spirit Medicine</v>
       </c>
       <c r="E18" t="str">
-        <v>档案 2-1 灵魂医学总介绍</v>
+        <v>灵魂医学总介绍</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -880,7 +880,7 @@
         <v>FILE 2-2 Evidence of existence of spirits(ghosts)</v>
       </c>
       <c r="E21" t="str">
-        <v>档案 2-2 鬼魂存在的证据</v>
+        <v>鬼魂存在的证据</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -949,7 +949,7 @@
         <v>File 2-3-2-1-1 Spiritual brain located in the flesh brain</v>
       </c>
       <c r="E24" t="str">
-        <v>档案 2-3-2-1-1  位于肉脑的灵脑器官</v>
+        <v>位于肉脑的灵脑器官</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -1018,7 +1018,7 @@
         <v>File 2-3-2-1-2 Spiritual-Brain Organs Located in the Heart</v>
       </c>
       <c r="E27" t="str">
-        <v>档案 2-3-2-1-2  位于心脏的灵脑器官</v>
+        <v>位于心脏的灵脑器官</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1087,7 +1087,7 @@
         <v>File 2-3-2-1-3 Spiritual-Brain Long-Term Memory Organ Located in the Cloud of the Ethereal Realm</v>
       </c>
       <c r="E30" t="str">
-        <v>档案 2-3-2-1-3  位于灵虚世界云端的灵脑记忆器官</v>
+        <v>位于灵虚世界云端的灵脑记忆器官</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -1156,7 +1156,7 @@
         <v>File 2-4-1-1 Overview,classification &amp; statistical data of America Spirit(ghost)</v>
       </c>
       <c r="E33" t="str">
-        <v>档案 2-4-1-1  美国鬼魂的概况，分类和统计学数据</v>
+        <v>美国鬼魂的概况，分类和统计学数据</v>
       </c>
       <c r="F33" t="str">
         <v/>
@@ -1225,7 +1225,7 @@
         <v>File 2-4-1-2 The disposition of American spirit (Ghost) &amp; Possibility of Organized Harm to Humans</v>
       </c>
       <c r="E36" t="str">
-        <v>档案 2-4-1-2  美国鬼魂的秉性，有组织侵害人类的可能性</v>
+        <v>美国鬼魂的秉性，有组织侵害人类的可能性</v>
       </c>
       <c r="F36" t="str">
         <v/>
@@ -1294,7 +1294,7 @@
         <v>File 2-4-1-3 The Physiological State of American spirit(ghost): Memory and Energy Metabolism</v>
       </c>
       <c r="E39" t="str">
-        <v>档案 2-4-1-3  美国鬼魂的生理状况之记忆和能量</v>
+        <v>美国鬼魂的生理状况之记忆和能量</v>
       </c>
       <c r="F39" t="str">
         <v/>
@@ -1363,7 +1363,7 @@
         <v>File 2-4-1-4 The Physiological State of American spirit(ghost): Thinking and Emotion</v>
       </c>
       <c r="E42" t="str">
-        <v>档案 2-4-1-4  美国鬼魂的生理状况之思维和情绪</v>
+        <v>美国鬼魂的生理状况之思维和情绪</v>
       </c>
       <c r="F42" t="str">
         <v/>
@@ -1429,10 +1429,10 @@
         <v>heading</v>
       </c>
       <c r="D45" t="str">
-        <v>File 2-4-1-5-1 The remote port organ (1)</v>
+        <v>File 2-4-1-5-1 American spirit (ghost)'s remote port organ (1)</v>
       </c>
       <c r="E45" t="str">
-        <v>档案 2-4-1-5-1 远程端口器官 （1）</v>
+        <v>美国鬼魂的远程交互器官（1）</v>
       </c>
       <c r="F45" t="str">
         <v/>
@@ -1498,10 +1498,10 @@
         <v>heading</v>
       </c>
       <c r="D48" t="str">
-        <v>File 2-4-1-5-2 The remote port organ (2)</v>
+        <v>File 2-4-1-5-2 American spirit (ghost)'s remote port organ (2)</v>
       </c>
       <c r="E48" t="str">
-        <v>档案 2-4-1-5-2 远程端口器官 （2）</v>
+        <v>美国鬼魂的远程交互器官（2）</v>
       </c>
       <c r="F48" t="str">
         <v/>
@@ -1570,7 +1570,7 @@
         <v>File 2-4-1-6-1 High Incidence of Depression Among Physicians and Psychologists, and the Reasons (1)</v>
       </c>
       <c r="E51" t="str">
-        <v>档案 2-4-1-6-1  医生和心理学家的抑郁症高发病率和原因（1）</v>
+        <v>医生和心理学家的抑郁症高发病率和原因（1）</v>
       </c>
       <c r="F51" t="str">
         <v/>
@@ -1639,7 +1639,7 @@
         <v>File 2-4-1-6-2 High Incidence of Depression Among Physicians and Psychologists, and the Reasons (2)</v>
       </c>
       <c r="E54" t="str">
-        <v>档案 2-4-1-6-2  医生和心理学家的抑郁症高发病率和原因（2）</v>
+        <v>医生和心理学家的抑郁症高发病率和原因（2）</v>
       </c>
       <c r="F54" t="str">
         <v/>
@@ -1708,7 +1708,7 @@
         <v>File 2-5-2-1-1 Pathological Principles of Schizophrenia and Dissociative Disorders (1)</v>
       </c>
       <c r="E57" t="str">
-        <v>档案 2-5-2-1-1  精神分裂症和分离性障碍的病理学原理（1）</v>
+        <v>精神分裂症和分离性障碍的病理学原理（1）</v>
       </c>
       <c r="F57" t="str">
         <v/>
@@ -1777,7 +1777,7 @@
         <v>File 2-5-2-1-2 Pathological Principles of Schizophrenia and Dissociative Disorders (2)</v>
       </c>
       <c r="E60" t="str">
-        <v>档案 2-5-2-1-2  精神分裂症和分离性障碍的病理学原理（2）</v>
+        <v>精神分裂症和分离性障碍的病理学原理（2）</v>
       </c>
       <c r="F60" t="str">
         <v/>
@@ -1846,7 +1846,7 @@
         <v>File 2-5-2-2 The Comprehensive Impact of Possessing spirit ghost on the Human Host's flesh body</v>
       </c>
       <c r="E63" t="str">
-        <v>档案 2-5-2-2  附体鬼魂对人类宿主肉体带来的全方位影响</v>
+        <v>附体鬼魂对人类宿主肉体带来的全方位影响</v>
       </c>
       <c r="F63" t="str">
         <v/>
@@ -1915,7 +1915,7 @@
         <v>File 2-5-2-3 Soul Pathology Principles &amp; Healing Strategies for Various Emotional Disorders</v>
       </c>
       <c r="E66" t="str">
-        <v>档案 2-5-2-3  各类情绪障碍灵魂病理学原理以及疗愈对策</v>
+        <v>各类情绪障碍灵魂病理学原理以及疗愈对策</v>
       </c>
       <c r="F66" t="str">
         <v/>
@@ -2766,7 +2766,7 @@
         <v>File 2-1 Abstract of Spirit Medicine</v>
       </c>
       <c r="E103" t="str">
-        <v>档案 2-1  灵魂医学总介绍</v>
+        <v>灵魂医学总介绍</v>
       </c>
       <c r="F103" t="str">
         <v/>
@@ -2858,7 +2858,7 @@
         <v>FILE 2-2 Evidence of existence of spirits(ghosts)</v>
       </c>
       <c r="E107" t="str">
-        <v>档案 2-2  鬼魂存在的证据</v>
+        <v>鬼魂存在的证据</v>
       </c>
       <c r="F107" t="str">
         <v/>
@@ -2950,7 +2950,7 @@
         <v>File 2-3-2-1-1 Spiritual brain located in the flesh brain</v>
       </c>
       <c r="E111" t="str">
-        <v>档案 2-3-2-1-1  位于肉脑的灵脑器官</v>
+        <v>位于肉脑的灵脑器官</v>
       </c>
       <c r="F111" t="str">
         <v/>
@@ -2996,7 +2996,7 @@
         <v>File 2-3-2-1-2 Spiritual-Brain Organs Located in the Heart</v>
       </c>
       <c r="E113" t="str">
-        <v>档案 2-3-2-1-2  位于心脏的灵脑器官</v>
+        <v>位于心脏的灵脑器官</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -3042,7 +3042,7 @@
         <v>File 2-3-2-1-3 Spiritual-Brain Long-Term Memory Organ Located in the Cloud of the Ethereal Realm</v>
       </c>
       <c r="E115" t="str">
-        <v>档案 2-3-2-1-3  位于灵虚世界云端的灵脑记忆器官</v>
+        <v>位于灵虚世界云端的灵脑记忆器官</v>
       </c>
       <c r="F115" t="str">
         <v/>
@@ -3134,7 +3134,7 @@
         <v>File 2-4-1-1 Overview,classification &amp; statistical data of America Spirit(ghost)</v>
       </c>
       <c r="E119" t="str">
-        <v>档案 2-4-1-1  美国鬼魂的概况，分类和统计学数据</v>
+        <v>美国鬼魂的概况，分类和统计学数据</v>
       </c>
       <c r="F119" t="str">
         <v/>
@@ -3180,7 +3180,7 @@
         <v>File 2-4-1-2 The disposition of American spirit (Ghost) &amp; Possibility of Organized Harm to Humans</v>
       </c>
       <c r="E121" t="str">
-        <v>档案 2-4-1-2  美国鬼魂的秉性，有组织侵害人类的可能性</v>
+        <v>美国鬼魂的秉性，有组织侵害人类的可能性</v>
       </c>
       <c r="F121" t="str">
         <v/>
@@ -3226,7 +3226,7 @@
         <v>File 2-4-1-3 The Physiological State of American spirit(ghost): Memory and Energy Metabolism</v>
       </c>
       <c r="E123" t="str">
-        <v>档案 2-4-1-3  美国鬼魂的生理状况之记忆和能量</v>
+        <v>美国鬼魂的生理状况之记忆和能量</v>
       </c>
       <c r="F123" t="str">
         <v/>
@@ -3272,7 +3272,7 @@
         <v>File 2-4-1-4 The Physiological State of American spirit(ghost): Thinking and Emotion</v>
       </c>
       <c r="E125" t="str">
-        <v>档案 2-4-1-4  美国鬼魂的生理状况之思维和情绪</v>
+        <v>美国鬼魂的生理状况之思维和情绪</v>
       </c>
       <c r="F125" t="str">
         <v/>
@@ -3315,10 +3315,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D127" t="str">
-        <v>File 2-4-1-5-1 The remote port organ (1)</v>
+        <v>File 2-4-1-5-1 American spirit (ghost)'s remote interaction organ (1)</v>
       </c>
       <c r="E127" t="str">
-        <v>档案 2-4-1-5-1 远程端口器官 （1）</v>
+        <v>美国鬼魂的远程交互器官（1）</v>
       </c>
       <c r="F127" t="str">
         <v/>
@@ -3361,10 +3361,10 @@
         <v>paragraph / other</v>
       </c>
       <c r="D129" t="str">
-        <v>File 2-4-1-5-2 The remote port organ (2)</v>
+        <v>File 2-4-1-5-2 American spirit (ghost)'s remote interaction organ (2)</v>
       </c>
       <c r="E129" t="str">
-        <v>档案 2-4-1-5-2  远程端口器官 （2）</v>
+        <v>美国鬼魂的远程交互器官（2）</v>
       </c>
       <c r="F129" t="str">
         <v/>
@@ -3410,7 +3410,7 @@
         <v>File 2-4-1-6-1 High Incidence of Depression Among Physicians and Psychologists, and the Reasons (1)</v>
       </c>
       <c r="E131" t="str">
-        <v>档案 2-4-1-6-1  医生和心理学家的抑郁症高发病率和原因（1）</v>
+        <v>医生和心理学家的抑郁症高发病率和原因（1）</v>
       </c>
       <c r="F131" t="str">
         <v/>
@@ -3456,7 +3456,7 @@
         <v>File 2-4-1-6-2 High Incidence of Depression Among Physicians and Psychologists, and the Reasons (2)</v>
       </c>
       <c r="E133" t="str">
-        <v>档案 2-4-1-6-2  医生和心理学家的抑郁症高发病率和原因（2）</v>
+        <v>医生和心理学家的抑郁症高发病率和原因（2）</v>
       </c>
       <c r="F133" t="str">
         <v/>
@@ -3548,7 +3548,7 @@
         <v>File 2-5-2-1-1 Pathological Principles of Schizophrenia and Dissociative Disorders (1)</v>
       </c>
       <c r="E137" t="str">
-        <v>档案 2-5-2-1-1  精神分裂症和分离性障碍的病理学原理（1）</v>
+        <v>精神分裂症和分离性障碍的病理学原理（1）</v>
       </c>
       <c r="F137" t="str">
         <v/>
@@ -3594,7 +3594,7 @@
         <v>File 2-5-2-1-2 Pathological Principles of Schizophrenia and Dissociative Disorders (2)</v>
       </c>
       <c r="E139" t="str">
-        <v>档案 2-5-2-1-2  精神分裂症和分离性障碍的病理学原理（2）</v>
+        <v>精神分裂症和分离性障碍的病理学原理（2）</v>
       </c>
       <c r="F139" t="str">
         <v/>
@@ -3640,7 +3640,7 @@
         <v>File 2-5-2-2 The Comprehensive Impact of Possessing spirit ghost on the Human Host's flesh body</v>
       </c>
       <c r="E141" t="str">
-        <v>档案 2-5-2-2  附体鬼魂对人类宿主肉体带来的全方位影响</v>
+        <v>附体鬼魂对人类宿主肉体带来的全方位影响</v>
       </c>
       <c r="F141" t="str">
         <v/>
@@ -3686,7 +3686,7 @@
         <v>File 2-5-2-3 Soul Pathology Principles &amp; Healing Strategies for Various Emotional Disorders</v>
       </c>
       <c r="E143" t="str">
-        <v>档案 2-5-2-3  各类情绪障碍灵魂病理学原理以及疗愈对策</v>
+        <v>各类情绪障碍灵魂病理学原理以及疗愈对策</v>
       </c>
       <c r="F143" t="str">
         <v/>

--- a/docs/page-copy/05-视频目录-灵体医学.xlsx
+++ b/docs/page-copy/05-视频目录-灵体医学.xlsx
@@ -3315,7 +3315,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D127" t="str">
-        <v>File 2-4-1-5-1 American spirit (ghost)'s remote interaction organ (1)</v>
+        <v>File 2-4-1-5-1 American spirit (ghost)'s remote port organ (1)</v>
       </c>
       <c r="E127" t="str">
         <v>美国鬼魂的远程交互器官（1）</v>
@@ -3361,7 +3361,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D129" t="str">
-        <v>File 2-4-1-5-2 American spirit (ghost)'s remote interaction organ (2)</v>
+        <v>File 2-4-1-5-2 American spirit (ghost)'s remote port organ (2)</v>
       </c>
       <c r="E129" t="str">
         <v>美国鬼魂的远程交互器官（2）</v>

--- a/docs/page-copy/05-视频目录-灵体医学.xlsx
+++ b/docs/page-copy/05-视频目录-灵体医学.xlsx
@@ -2041,7 +2041,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>spiritMedicineOfficialOutline[2].fileLabel</v>
+        <v>spiritMedicineOfficialOutline[3].fileLabel</v>
       </c>
       <c r="B72" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>spiritMedicineOfficialOutline[2].heading</v>
+        <v>spiritMedicineOfficialOutline[3].heading</v>
       </c>
       <c r="B73" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>spiritMedicineOfficialOutline[2].subsections[0].code</v>
+        <v>spiritMedicineOfficialOutline[3].subsections[0].code</v>
       </c>
       <c r="B74" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>spiritMedicineOfficialOutline[2].subsections[0].title</v>
+        <v>spiritMedicineOfficialOutline[3].subsections[0].title</v>
       </c>
       <c r="B75" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>spiritMedicineOfficialOutline[2].subsections[1].code</v>
+        <v>spiritMedicineOfficialOutline[3].subsections[1].code</v>
       </c>
       <c r="B76" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>spiritMedicineOfficialOutline[2].subsections[1].title</v>
+        <v>spiritMedicineOfficialOutline[3].subsections[1].title</v>
       </c>
       <c r="B77" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>spiritMedicineOfficialOutline[3].fileLabel</v>
+        <v>spiritMedicineOfficialOutline[2].fileLabel</v>
       </c>
       <c r="B78" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>spiritMedicineOfficialOutline[3].heading</v>
+        <v>spiritMedicineOfficialOutline[2].heading</v>
       </c>
       <c r="B79" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[0].code</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[0].code</v>
       </c>
       <c r="B80" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2248,7 +2248,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[0].title</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[0].title</v>
       </c>
       <c r="B81" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2271,7 +2271,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[1].code</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[1].code</v>
       </c>
       <c r="B82" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[1].title</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[1].title</v>
       </c>
       <c r="B83" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[2].code</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[2].code</v>
       </c>
       <c r="B84" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[2].title</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[2].title</v>
       </c>
       <c r="B85" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2363,7 +2363,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[3].code</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[3].code</v>
       </c>
       <c r="B86" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[3].title</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[3].title</v>
       </c>
       <c r="B87" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[4].code</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[4].code</v>
       </c>
       <c r="B88" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[4].title</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[4].title</v>
       </c>
       <c r="B89" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2455,7 +2455,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[5].code</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[5].code</v>
       </c>
       <c r="B90" t="str">
         <v>灵体医学 / 完整目录</v>
@@ -2478,7 +2478,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>spiritMedicineOfficialOutline[3].subsections[5].title</v>
+        <v>spiritMedicineOfficialOutline[2].subsections[5].title</v>
       </c>
       <c r="B91" t="str">
         <v>灵体医学 / 完整目录</v>
